--- a/artfynd/A 9458-2026 artfynd.xlsx
+++ b/artfynd/A 9458-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -912,6 +912,131 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133594349</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58332</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sakris-Pettersbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>583966</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7026417</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9458-2026 artfynd.xlsx
+++ b/artfynd/A 9458-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>120307632</v>
       </c>
       <c r="B2" t="n">
-        <v>57333</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,12 +795,7 @@
         <v>120744832</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1037,6 +1027,247 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133594350</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gröningsåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>584032</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7026366</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>05:47</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Andreas Bernhold</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120307595</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gröningsåsen, Gröningsåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>584112</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7026299</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9458-2026 artfynd.xlsx
+++ b/artfynd/A 9458-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120307632</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120744832</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133594349</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1151,6 +1171,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133594350</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,8 +1292,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120307595</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>